--- a/2022 data/excel_outputs/363_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/363_boothwise_data.xlsx
@@ -14,777 +14,1260 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="438">
   <si>
     <t>AC 363 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>######## ######## ######## ####### ;######ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ######</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ####### ;#######ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ##### ########</t>
-  </si>
-  <si>
-    <t>##0##0##### #### ######</t>
-  </si>
-  <si>
-    <t>##0##0##### #### ####</t>
-  </si>
-  <si>
-    <t>##0##0##### #### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### ##### ###### #0 ###</t>
-  </si>
-  <si>
-    <t>######## ####### #### ##### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ## #### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ## #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ##### ####</t>
-  </si>
-  <si>
-    <t>######## ####### #### #### ######</t>
-  </si>
-  <si>
-    <t>######## ####### #### #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>##0##0##### ######## ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ######## #######</t>
-  </si>
-  <si>
-    <t>##0##0##### ######## ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>###### ### #####</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ######## ######</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####</t>
-  </si>
-  <si>
-    <t>######## ####### #### ####### ## ####</t>
-  </si>
-  <si>
-    <t>######## ####### ########## ######</t>
-  </si>
-  <si>
-    <t>######## ####### ########## #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### ##### #######</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### #######</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### #######</t>
-  </si>
-  <si>
-    <t>######## ####### #######</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ##### ####### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ##### ####### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ##### ####### ####</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #### #0</t>
-  </si>
-  <si>
-    <t>##0##0##### ######## ##### ###### ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ######## ##### ###### ####</t>
-  </si>
-  <si>
-    <t>##0##0##### ######## ##### ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ###### ### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### ### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ####### #0</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##### ##### #######</t>
-  </si>
-  <si>
-    <t>#### ####### ##### ##### ##### ####### ######</t>
-  </si>
-  <si>
-    <t>#### ####### ##### ##### ##### ####### ####</t>
-  </si>
-  <si>
-    <t>#### ####### ##### ##### ##### ####### #######</t>
-  </si>
-  <si>
-    <t>####### ###### #### ###### ######## ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### ##### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ##0 2 ######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ##0 # #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0 1 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0 1 #######</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ##### ####### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ##### ####### #######</t>
-  </si>
-  <si>
-    <t>##0##0 #0##0 ######## ######</t>
-  </si>
-  <si>
-    <t>##0##0 #0##0 ######## ####</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ######## #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
-  </si>
-  <si>
-    <t>######## ###### #### #### ##### ##### ####### ######</t>
-  </si>
-  <si>
-    <t>######## ####### #### #### ##### ##### ####### ####</t>
-  </si>
-  <si>
-    <t>######## ####### ######## ##### ##### ####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ##### ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ##### ###### #0</t>
-  </si>
-  <si>
-    <t>##0##0##### ########## ##### ###### ##0</t>
-  </si>
-  <si>
-    <t>##0##0##### ########## ##### ###### #0</t>
-  </si>
-  <si>
-    <t>######## #### ##0##0 ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #0</t>
-  </si>
-  <si>
-    <t>#0#0### #0##0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>#0#0### #0##0##0 ###### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ;#########ddh ######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ;#########ddh ####</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ;#########ddh #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### ###### #### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##0 1</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ### ####### ### ######## ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ### ####### ### ######## #######</t>
-  </si>
-  <si>
-    <t>###### #0##0 ######### ######</t>
-  </si>
-  <si>
-    <t>###### #0##0 ######### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### ##### #########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### 1 #######</t>
-  </si>
-  <si>
-    <t>###### ### ###### ######</t>
-  </si>
-  <si>
-    <t>###### ### ###### #######</t>
-  </si>
-  <si>
-    <t>#0##0#0##0 ####### ###### 1</t>
-  </si>
-  <si>
-    <t>#0##0#0##0 ####### ###### 1 ####</t>
-  </si>
-  <si>
-    <t>#0##0#0##0 ####### ###### 2</t>
-  </si>
-  <si>
-    <t>#0##0#0##0 ####### ####### 1</t>
-  </si>
-  <si>
-    <t>#0##0#0##0 ####### ####### 2</t>
-  </si>
-  <si>
-    <t>#0##0#0##0 ####### ####### # #0</t>
-  </si>
-  <si>
-    <t>####0##0 ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ## #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ## #### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##0 2 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##0 2 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ### #0</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ###### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ###### ####</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ######</t>
-  </si>
-  <si>
-    <t>###### ### ####### ######</t>
-  </si>
-  <si>
-    <t>###### ### ####### #######</t>
-  </si>
-  <si>
-    <t>#0##0##0 ####### #0##0 ####### ##0</t>
-  </si>
-  <si>
-    <t>#0##0##0 ####### #0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>#0##0##0 ####### #0##0 ####### #0</t>
-  </si>
-  <si>
-    <t>######## ####### ######## ####</t>
-  </si>
-  <si>
-    <t>### #### #### ##### ##0 ####### #######</t>
-  </si>
-  <si>
-    <t>### #### #### ##### ##0 ####### ####</t>
-  </si>
-  <si>
-    <t>### #### #### ##### ##0 ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ## ##### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ## ##### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ## 1 ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ## 1 ######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ##0.2 ######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ##0.2 ####</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ##0.2 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ## #####</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>######## ####### ######### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ######### ####</t>
-  </si>
-  <si>
-    <t>######## ####### ######### #######</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ### ######### ##0</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ### ######### ####</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ### ######### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0</t>
-  </si>
-  <si>
-    <t>##0 ###### ######## ##### ###### ###### ######</t>
-  </si>
-  <si>
-    <t>##0 ###### ######## ##### ###### ###### #######</t>
-  </si>
-  <si>
-    <t>######## ####### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>######## ####### ############ ######</t>
-  </si>
-  <si>
-    <t>######## ####### ############ ####</t>
-  </si>
-  <si>
-    <t>######## ####### ############ #######</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ######</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ####</t>
-  </si>
-  <si>
-    <t>########### ########### ####### #0</t>
-  </si>
-  <si>
-    <t>########### ########### ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #0</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### ## #####</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ### #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ### #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ### ## #### ##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #######</t>
-  </si>
-  <si>
-    <t>#### #0### ##0#0##0 ###### #0</t>
-  </si>
-  <si>
-    <t>#### #0### #0##0 ###### ##0</t>
-  </si>
-  <si>
-    <t>#### #0 ### #0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>#### #0 ### #0##0 ###### ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ## ##### ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ## ##### ###### #0</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ### ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ### ###### # 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ### ###### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ############ ###### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ############ ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ############ ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ### ## #### ##### ############ ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ### ## #### ##### ############ ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0 2</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #######</t>
-  </si>
-  <si>
-    <t>##### ######## ######## #### ### ### ##### ############ ###### #######</t>
-  </si>
-  <si>
-    <t>##### ######## ######## #### ### ### ##### ############ ###### ######</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ### #######</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####### #0</t>
-  </si>
-  <si>
-    <t>######## ############ ####### ######</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####### ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### ## #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### ## #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##0</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ####### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #### ## ####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ############ ###### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ############ ###### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ############ ###### #0</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0########### #0</t>
-  </si>
-  <si>
-    <t>####0##0########### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### ####</t>
-  </si>
-  <si>
-    <t>##0##### ######## ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ####### #### ##### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ####### #### ##### #0</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ###</t>
-  </si>
-  <si>
-    <t>####0##0 #### ## #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ## #### #######</t>
+    <t>1.CHANCHAN THIVACHAMSACHANAT CHMEBIPAUP MMEJ</t>
+  </si>
+  <si>
+    <t>PASCHIMI 2-P.P. EAST BHOPALPUR</t>
+  </si>
+  <si>
+    <t>PASCHIMI 3-P.P. WEST BHOPALPUR</t>
+  </si>
+  <si>
+    <t>PURVIRAMPUR 4-P.P.</t>
+  </si>
+  <si>
+    <t>MAGRIV SATHIT 5-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL DATTAHA 6-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL MIDDLE 7-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 8-P.P. DATAHA SHIVPUR</t>
+  </si>
+  <si>
+    <t>SATHIT 9-P.P. SHIVPUR</t>
+  </si>
+  <si>
+    <t>SATHITCHHAPARA 10-P.P. GRAM</t>
+  </si>
+  <si>
+    <t>SARIW CHHAPARA 11-P.P. EAST</t>
+  </si>
+  <si>
+    <t>SARIW CHHAPARA 12-P.P. WEST</t>
+  </si>
+  <si>
+    <t>SARIW ASMANPUR 13-P.P. MIDDLE</t>
+  </si>
+  <si>
+    <t>SATHIT GRAM 14-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL NAVAKA 15-P.P.</t>
+  </si>
+  <si>
+    <t>JAMDHARWA 16-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL HIGH 17-JUNIOR</t>
+  </si>
+  <si>
+    <t>SCHOOL HIGH 18-JUNIOR</t>
+  </si>
+  <si>
+    <t>SCHOLL HIGH 19-JUNIOR</t>
+  </si>
+  <si>
+    <t>SCHOLL HIGH 20-JUNIOR</t>
+  </si>
+  <si>
+    <t>SCHOOL 21-P.P.</t>
+  </si>
+  <si>
+    <t>VASHISHATH 22-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL HIGH 23-JUNIOR</t>
+  </si>
+  <si>
+    <t>SCHOOL HIGH 24-JUNIOR</t>
+  </si>
+  <si>
+    <t>SCHOOL 25-P.P. BHAKHAR</t>
+  </si>
+  <si>
+    <t>PANCHAYAT</t>
+  </si>
+  <si>
+    <t>BHAWAN 27-P.P. KHARIKA KHARIKA</t>
+  </si>
+  <si>
+    <t>P.P. CHAUBEY</t>
+  </si>
+  <si>
+    <t>CHHAPARA 29-P.P. NORTH CHAUBEY</t>
+  </si>
+  <si>
+    <t>CHHAPARA SOUTH 30-P.P.</t>
+  </si>
+  <si>
+    <t>KANCHANPUR 31-P.P.</t>
+  </si>
+  <si>
+    <t>KANCHANPUR 32-P.P. CHHERDIH</t>
+  </si>
+  <si>
+    <t>SOUTHCHHERDIH 33-P.P.</t>
+  </si>
+  <si>
+    <t>WEST CHHERDIH 34-P.P.</t>
+  </si>
+  <si>
+    <t>MIDDLE 35-P.P. RAMPUR</t>
+  </si>
+  <si>
+    <t>EAST RAMPUR 36-P.P.</t>
+  </si>
+  <si>
+    <t>WEST 37-P.P.</t>
+  </si>
+  <si>
+    <t>MUNCHHAPARA 38-P.P.</t>
+  </si>
+  <si>
+    <t>MUNCHHAPARA 39-P.P. GANGA</t>
+  </si>
+  <si>
+    <t>PANDEY 40-P.P. KA TOLA LAXMIPUR</t>
+  </si>
+  <si>
+    <t>P.P. MANSINGH</t>
+  </si>
+  <si>
+    <t>CHHAPARA 42-P.P. URF MANSINGH</t>
+  </si>
+  <si>
+    <t>CHHAPARAHIGH 43-JUNIOR URF</t>
+  </si>
+  <si>
+    <t>SCHOOL VIGAHI 44-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL VIGAHI 45-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 46-P.P. VIGAHI VIGAHI</t>
+  </si>
+  <si>
+    <t>TOWN INTER</t>
+  </si>
+  <si>
+    <t>COLLEG,BALLIA,N 48-P.P. KATHAHI</t>
+  </si>
+  <si>
+    <t>SOUTHSONVANI 49-P.P.</t>
+  </si>
+  <si>
+    <t>EAST SONWANI 50-P.P.</t>
+  </si>
+  <si>
+    <t>MIDDLE 51-P.P. SONWANI</t>
+  </si>
+  <si>
+    <t>EAST 52-P.P.</t>
+  </si>
+  <si>
+    <t>SAMARTHPAH 53-P.P. KRIPALPUR</t>
+  </si>
+  <si>
+    <t>PURV M.V.</t>
+  </si>
+  <si>
+    <t>DUDHAILA 55-PURV EAST M.V.</t>
+  </si>
+  <si>
+    <t>DUDHAILA 56-P.P. WEST DUDHAILA</t>
+  </si>
+  <si>
+    <t>P.P. BADILPUR</t>
+  </si>
+  <si>
+    <t>EAST 58-P.P.</t>
+  </si>
+  <si>
+    <t>HRIDAYCHAK 59-P.P. BADILPUR</t>
+  </si>
+  <si>
+    <t>SATHITGAIGHAT 60-P.P.</t>
+  </si>
+  <si>
+    <t>61.CHANCHAN LAMPAHIMJ DAPAKAKASAM</t>
+  </si>
+  <si>
+    <t>MIDDLE 62-P.P. MUDADIH</t>
+  </si>
+  <si>
+    <t>SATHITMUDADIH 63-P.P. MUDADIH</t>
+  </si>
+  <si>
+    <t>SATHITGAIGHAT 64-P.P. MUDADIH</t>
+  </si>
+  <si>
+    <t>SATHITRUDRAPUR 65-P.P. MUDADIH</t>
+  </si>
+  <si>
+    <t>P.P. MAUDADIH</t>
+  </si>
+  <si>
+    <t>P.P. BABUBEL</t>
+  </si>
+  <si>
+    <t>SATHITBABUBEL 68-P.P. BAGHAUCH</t>
+  </si>
+  <si>
+    <t>SATHITBELHARI 69-P.P. BAGHAUCH</t>
+  </si>
+  <si>
+    <t>WEST BELHARI 70-P.P.</t>
+  </si>
+  <si>
+    <t>MIDDLE 71-P.P. BELHARI</t>
+  </si>
+  <si>
+    <t>EAST 72-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL HIGH 73-JUNIOR</t>
+  </si>
+  <si>
+    <t>SCHOOL 74-P.P.</t>
+  </si>
+  <si>
+    <t>SHUKALCHHAPARA 75-P.P.</t>
+  </si>
+  <si>
+    <t>SHUKALCHHAPARA 76-P.P.</t>
+  </si>
+  <si>
+    <t>DHARAMPURA 77-P.P. GARYA</t>
+  </si>
+  <si>
+    <t>SATHITGARYA 78-P.P. BELHARI</t>
+  </si>
+  <si>
+    <t>SATHITMAJHAUA 79-P.P. BELHARI</t>
+  </si>
+  <si>
+    <t>EAST MAJHAUA 80-P.P.</t>
+  </si>
+  <si>
+    <t>WEST MAJHAUA 81-P.P.</t>
+  </si>
+  <si>
+    <t>EAST NAYA 82-P.P. MAJHAUA</t>
+  </si>
+  <si>
+    <t>WEST NAYA 83-P.P. MALIKPURA</t>
+  </si>
+  <si>
+    <t>P.P.</t>
+  </si>
+  <si>
+    <t>NARAYANPUR 85-P.P.</t>
+  </si>
+  <si>
+    <t>NARAYANPUR 86-P.P.</t>
+  </si>
+  <si>
+    <t>NARAYANPUR 87-P.P. PIYARAUTA</t>
+  </si>
+  <si>
+    <t>EAST PIYARAUTA 88-P.P.</t>
+  </si>
+  <si>
+    <t>MIDDLE 89-P.P. PIYARAUTA</t>
+  </si>
+  <si>
+    <t>WEST DIGHAR 90-P.P.</t>
+  </si>
+  <si>
+    <t>EAST DIGHAR 91-P.P.</t>
+  </si>
+  <si>
+    <t>MIDDLE 92-P.P. DIGHAR</t>
+  </si>
+  <si>
+    <t>WEST CONVENT 93-S.M.</t>
+  </si>
+  <si>
+    <t>SCHOOLCANVENT 94-S.M.</t>
+  </si>
+  <si>
+    <t>SCHOOLCONVENT 95-S.M.</t>
+  </si>
+  <si>
+    <t>SCHOOL 96-P.P. DURJANPUR</t>
+  </si>
+  <si>
+    <t>SATHIT GANGAPUR 97-SADHAN</t>
+  </si>
+  <si>
+    <t>SAHAKARI SAMITI 98-SADHAN</t>
+  </si>
+  <si>
+    <t>SAHAKARI SAMITI 99-DHUPARAM</t>
+  </si>
+  <si>
+    <t>PYARI DEVI 100-DHUPARAM</t>
+  </si>
+  <si>
+    <t>PYARI DEVI 101-P.P. SHIVCHAK</t>
+  </si>
+  <si>
+    <t>TANDI 102-P.P.NAUKAGAO NAUKAGAO</t>
+  </si>
+  <si>
+    <t>EAST 103-P.P. NAUKAGAO</t>
+  </si>
+  <si>
+    <t>WEST 104-P.P.</t>
+  </si>
+  <si>
+    <t>DAYACHHAPARA 105-P.P.</t>
+  </si>
+  <si>
+    <t>DAYACHHAPARA 106-P.P.</t>
+  </si>
+  <si>
+    <t>DAYACHHAPARA 107-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 108-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 109-P.P.</t>
+  </si>
+  <si>
+    <t>BUDHANCHAK 110-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 111-P.P.</t>
+  </si>
+  <si>
+    <t>DALAPATPUR 112-P.P.</t>
+  </si>
+  <si>
+    <t>DALAPATPUR 113-P.P. INTER</t>
+  </si>
+  <si>
+    <t>COLLAGE 114-P.N. INTER</t>
+  </si>
+  <si>
+    <t>COLLAGE 115-P.N. INTER</t>
+  </si>
+  <si>
+    <t>COLLAGE 116-P.P. P. N. INTER</t>
+  </si>
+  <si>
+    <t>COLLAGE 117-P.P. PRASAD</t>
+  </si>
+  <si>
+    <t>CHHAPARA 118-P.P.</t>
+  </si>
+  <si>
+    <t>SUGHARCHHAPAR 119-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 120-P.VIDHYALAY</t>
+  </si>
+  <si>
+    <t>SUGHARCHHAPAR 121-P.P. RAMPUR</t>
+  </si>
+  <si>
+    <t>MISHRARAMPUR 122-P.P. SATHIT</t>
+  </si>
+  <si>
+    <t>MISHRA SATHIT 123-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 124-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 125-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 126-P.P.</t>
+  </si>
+  <si>
+    <t>TENGARAHI 127-P.P.</t>
+  </si>
+  <si>
+    <t>TENGARAHI SOUTH 128-P.P.</t>
+  </si>
+  <si>
+    <t>TENGARAHI EAST 129-ADARSH P.P.</t>
+  </si>
+  <si>
+    <t>CHANPUR EAST 130-ADARSH P.P.</t>
+  </si>
+  <si>
+    <t>CHANDPUR P.P. 131-ADARSH</t>
+  </si>
+  <si>
+    <t>132.TAMUPAIMS THAMIM SHRANADAPAVAT BHPAHI AIBIVAVAS BIMDAKACHANAT</t>
+  </si>
+  <si>
+    <t>BABA JUNIOR HIGH 133-P.P.</t>
+  </si>
+  <si>
+    <t>GOVINDPUR 134-P.P.</t>
+  </si>
+  <si>
+    <t>CHARAJPURA 135-P.P.</t>
+  </si>
+  <si>
+    <t>SHRIPALPUR 136-P.P. LAXMIPUR</t>
+  </si>
+  <si>
+    <t>SAVANCHHAPARA 138-P.P.</t>
+  </si>
+  <si>
+    <t>SAVANCHHAPARA 139-P.P.</t>
+  </si>
+  <si>
+    <t>CHIRANJICHHAPAR 140-P.P.</t>
+  </si>
+  <si>
+    <t>CHIRANJICHHAPAR 141-A.N.DEV U.M.V.</t>
+  </si>
+  <si>
+    <t>BAHUARA SOUTH 142-A.N.DEV U.M.V.</t>
+  </si>
+  <si>
+    <t>BAHUARA NORTH 143-P.P.</t>
+  </si>
+  <si>
+    <t>JAICHHAPARA 144-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 145-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOLJAGDIPUR 146-P.P.</t>
+  </si>
+  <si>
+    <t>JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL NAURNGA 148-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 149-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 150-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 151-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 152-P.P.</t>
+  </si>
+  <si>
+    <t>BHAGWANPUR 153-P.P. SHIVPUR</t>
+  </si>
+  <si>
+    <t>KAPUR DIAR 154-P.P. EAST SHIVPUR</t>
+  </si>
+  <si>
+    <t>KAPUR DIAR 155-P.P. WEST SEMARIA</t>
+  </si>
+  <si>
+    <t>P.P. GARERIYA</t>
+  </si>
+  <si>
+    <t>SATHIT DALAKI 157-P.P. SHIVPURNO</t>
+  </si>
+  <si>
+    <t>158-P.P. LACHHU</t>
+  </si>
+  <si>
+    <t>TOLA NORTH 159-P.P. LACHHU</t>
+  </si>
+  <si>
+    <t>TOLA SOUTH 160-P.P. ARAJI MAFI</t>
+  </si>
+  <si>
+    <t>BAL GOVIND 161-P.P. ARAJIRAI MAFI</t>
+  </si>
+  <si>
+    <t>BAL GOVIND RAI 162-RAMNATH</t>
+  </si>
+  <si>
+    <t>INTER COLLAGE 163-RAMNATH</t>
+  </si>
+  <si>
+    <t>INTER COLLAGE 164-P.P.</t>
+  </si>
+  <si>
+    <t>HRIDAYCHAK 165-P.P. GARERIYA</t>
+  </si>
+  <si>
+    <t>SATHIT VAJIDPUR 166-P.P. GRAM</t>
+  </si>
+  <si>
+    <t>NORTH 167-P.P.</t>
+  </si>
+  <si>
+    <t>DALANCHHAPARA 168-P.P. RAMPUR</t>
+  </si>
+  <si>
+    <t>KODARAHA 169-PANCHAYAT</t>
+  </si>
+  <si>
+    <t>BHAWAN 170-P.P. RAMPU RAMPUR</t>
+  </si>
+  <si>
+    <t>SCHOOL DOKATI 172-JUNIOT HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL DOKATI 173-JUNIOT HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL DOKATI 174-P.P.</t>
+  </si>
+  <si>
+    <t>MURALICHHAPARA 175-P.P.</t>
+  </si>
+  <si>
+    <t>MURALICHHAPARA 176-M.G.I.C.</t>
+  </si>
+  <si>
+    <t>DALANCHHAPARA 177-M.G.I.C.</t>
+  </si>
+  <si>
+    <t>DALANCHHAPARA 178-M.G.I.C.</t>
+  </si>
+  <si>
+    <t>DALANCHHAPARA 179-M.G.I.C.</t>
+  </si>
+  <si>
+    <t>DALANCHHAPARA 180-M.G.I.C.</t>
+  </si>
+  <si>
+    <t>DALANCHHAPARA 181-P.P. DALAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA 182-P.P. NO 2 MANIRAI</t>
+  </si>
+  <si>
+    <t>KA DERA 183-P.P.</t>
+  </si>
+  <si>
+    <t>KARANCHHAPARA 184-P.P.</t>
+  </si>
+  <si>
+    <t>KARANCHHAPARA 185-P.P.</t>
+  </si>
+  <si>
+    <t>KARANCHHAPARA 186-P.P.</t>
+  </si>
+  <si>
+    <t>KARANCHHAPARA 187-P.P.</t>
+  </si>
+  <si>
+    <t>KARANCHHAPARA 188-P.P.</t>
+  </si>
+  <si>
+    <t>KARANCHHAPARA 189-P.P. DHATURI</t>
+  </si>
+  <si>
+    <t>TOLA NORTH 190-P.P. DHARUTI</t>
+  </si>
+  <si>
+    <t>TOLA SOUTH 191-P.P. KAKAN</t>
+  </si>
+  <si>
+    <t>TOLA 192-P.P.</t>
+  </si>
+  <si>
+    <t>SONAKIBHAT 193-P.P.</t>
+  </si>
+  <si>
+    <t>SONAKIBHAT 194-PANCHAYAT</t>
+  </si>
+  <si>
+    <t>BHAWAN 195-P.P. SUKRAULI</t>
+  </si>
+  <si>
+    <t>SHRIPATIPUR 197-P.P.</t>
+  </si>
+  <si>
+    <t>SHRIPATIPUR 198-P.P. SHIVPUR</t>
+  </si>
+  <si>
+    <t>NAURANGA 199-P.P. EAST SHIVPUR</t>
+  </si>
+  <si>
+    <t>NAURANGA 200-P.P. SHIVPUR</t>
+  </si>
+  <si>
+    <t>NAURANGA 201-P.P. WEST SAWAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA EAST 202-PANCHAYAT</t>
+  </si>
+  <si>
+    <t>20 3NDACHAT|CH|CH SHRCH|J|CH|BBH|AI|DAK|CH CHK|SHR|D|J THAT|AI|AI|D|BH|D AIBHT|DANDAI|BBH|CH|J DADAMSHR</t>
+  </si>
+  <si>
+    <t>INTER COLLAGE 204-A.J.V. KRIPLANI</t>
+  </si>
+  <si>
+    <t>INTER COLLAGE 205-A.J.V.KRIPLANI</t>
+  </si>
+  <si>
+    <t>INTER COLLEGE 206-P.P. CHAKIA</t>
+  </si>
+  <si>
+    <t>NORTH CHAKIA 207-P.P.</t>
+  </si>
+  <si>
+    <t>MIDDLECHAKIA 208-P.P.</t>
+  </si>
+  <si>
+    <t>SOUTH 209-P.P.</t>
+  </si>
+  <si>
+    <t>CHAKGIRDHAR 210-P.P.</t>
+  </si>
+  <si>
+    <t>CHAKGIRDHAR 211-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 212-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOLSABALPUR 213-P.P.</t>
+  </si>
+  <si>
+    <t>SCHOOL TALIBPUR 215-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL TALIBPUR 216-AMAR SHAHID</t>
+  </si>
+  <si>
+    <t>KAUSHAL KUMAR 217-AMAR SHAHID</t>
+  </si>
+  <si>
+    <t>KAUSHAL SHAHID 218-AMAR</t>
+  </si>
+  <si>
+    <t>KAUSHAL KUMAR 219-P.P.</t>
+  </si>
+  <si>
+    <t>DUKHAHARAN GIRI 220-P.P.</t>
+  </si>
+  <si>
+    <t>SHRINAGAR NO 1 221-P.P.</t>
+  </si>
+  <si>
+    <t>SHRINAGAR NO 1 222-P.P.</t>
+  </si>
+  <si>
+    <t>SHRINAGAR NO 1 223-P.P.</t>
+  </si>
+  <si>
+    <t>SHRINAGAR NO 1 224-P.P.</t>
+  </si>
+  <si>
+    <t>SHRINAGAR NO 2 225-P.P.</t>
+  </si>
+  <si>
+    <t>SHRINAGAR NO 2 226-P.P.</t>
+  </si>
+  <si>
+    <t>DALANCHHAPARA 227-P.P.</t>
+  </si>
+  <si>
+    <t>DALANCHHAPARA 228-P.P.</t>
+  </si>
+  <si>
+    <t>SHRINAGAR NAI 229-P.P.</t>
+  </si>
+  <si>
+    <t>HANUMANGANJ 230-P.P.</t>
+  </si>
+  <si>
+    <t>DURJANPUT EAST 231-P.P.</t>
+  </si>
+  <si>
+    <t>DURAJANPUT 232-P.P.</t>
+  </si>
+  <si>
+    <t>DURAJANPUR 233-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL ADARSH 234-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL ADARSH 235-P.P.</t>
+  </si>
+  <si>
+    <t>SUREMANPUR 236-P.P.</t>
+  </si>
+  <si>
+    <t>SUREMANPUR 237-PANCHAYAT</t>
+  </si>
+  <si>
+    <t>BHAWAN 238-PANCHAYAT</t>
+  </si>
+  <si>
+    <t>BHAWAN 239-P.P.</t>
+  </si>
+  <si>
+    <t>MADHUBANI 240-P.P.</t>
+  </si>
+  <si>
+    <t>MADHUBANI 241-P.P.</t>
+  </si>
+  <si>
+    <t>MADHUBANI 242-DR. BHIMRAO</t>
+  </si>
+  <si>
+    <t>AMBEDKAR 243-P.P.</t>
+  </si>
+  <si>
+    <t>BAIJNATHPUR 244-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOLSHIVAL 245-P.P. MANGAR</t>
+  </si>
+  <si>
+    <t>UPADHAYAYPUR 247-P.P.</t>
+  </si>
+  <si>
+    <t>CHAICHHAPARA 248-P.P.</t>
+  </si>
+  <si>
+    <t>CHAICHHAPARA 249-P.P.</t>
+  </si>
+  <si>
+    <t>GONIYACHHAPARA 250-P.P.</t>
+  </si>
+  <si>
+    <t>GONIYACHHAPARA 251-P.P.</t>
+  </si>
+  <si>
+    <t>VISHUNPURA 252-P.P.</t>
+  </si>
+  <si>
+    <t>VISHUNPURA 253-P.P.</t>
+  </si>
+  <si>
+    <t>ADHISIJHUA 254-P.P.</t>
+  </si>
+  <si>
+    <t>BHIKHACHHAPARA 255-P.P.</t>
+  </si>
+  <si>
+    <t>BHIKACHHAPARA 256-SUDISHATPURI</t>
+  </si>
+  <si>
+    <t>M.V. RANIGANJ 257-SUDISHATPURI</t>
+  </si>
+  <si>
+    <t>M.V. RANGANJ 258-P.P.</t>
+  </si>
+  <si>
+    <t>BAIJNATHCHHAPA 259-P.P. RANIGANJ</t>
+  </si>
+  <si>
+    <t>WEST JHANDA 260-P.P.</t>
+  </si>
+  <si>
+    <t>BHARATI 261-P.P. KE RANIGANJ</t>
+  </si>
+  <si>
+    <t>BAZAR RANIGANJ 262-P.P.</t>
+  </si>
+  <si>
+    <t>BAZAR RANIGANJ 263-P.P.</t>
+  </si>
+  <si>
+    <t>MIDDLEBHARAT 264-P.P.</t>
+  </si>
+  <si>
+    <t>CHHAPARA 265-P.P. BIN KE</t>
+  </si>
+  <si>
+    <t>TOLA SATHIT 266-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOLMIRJAPUR 267-P.P. MIRJAPUR</t>
+  </si>
+  <si>
+    <t>BABA LAXMAN</t>
+  </si>
+  <si>
+    <t>DAS I.C. BAIRIA 269-BABA LAXMAN</t>
+  </si>
+  <si>
+    <t>DAS I.C. BAIRIA 270-BABA LAXMAN</t>
+  </si>
+  <si>
+    <t>DAS I.C. BAIRIA 271-BABA LAXMAN</t>
+  </si>
+  <si>
+    <t>DAS I.C. BAIRIA 272-BABA LAXMAN</t>
+  </si>
+  <si>
+    <t>DAS I.C. BAIRIA 273-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>274.RANADAPAVAT BHPAHI AIBIVAVAS THAMPATAPAM DAPAKAKASAM</t>
+  </si>
+  <si>
+    <t>SCHOOL BAIRIA 275-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL BAIRIA 276-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL EAST 277-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOLMISHRA 278-P.P. EAST KE</t>
+  </si>
+  <si>
+    <t>MATHIAMISHRA 279-P.P. BAIRIA KE</t>
+  </si>
+  <si>
+    <t>MATHIABAIRIA 280-P.P. BAIRIA</t>
+  </si>
+  <si>
+    <t>WEST BAIRIA 281-P.P.</t>
+  </si>
+  <si>
+    <t>EAST JAGDEVA 282-P.P.</t>
+  </si>
+  <si>
+    <t>GAO SABHA 283-P.P. BAIRIA JAGDEVA</t>
+  </si>
+  <si>
+    <t>GAO SABHA 284-P.P. BAIRIA JAGDEVA</t>
+  </si>
+  <si>
+    <t>GAO SABHA BAIRIA 285-P.P.</t>
+  </si>
+  <si>
+    <t>IBRAHIMABAD 286-P.P.</t>
+  </si>
+  <si>
+    <t>IBRAHIMABAD 287-P.P.</t>
+  </si>
+  <si>
+    <t>IBRAHIMABAD 288-P.P. MUJ KE</t>
+  </si>
+  <si>
+    <t>DERA SATHIT 289-P.P. NEKARAI</t>
+  </si>
+  <si>
+    <t>NO 1 290-P.P. NEKARAI</t>
+  </si>
+  <si>
+    <t>NO 2 291-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL SHOBHA 292-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL SHOBHA 293-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL SHOBHA 294-P.P.</t>
+  </si>
+  <si>
+    <t>MATHDHAJJU GIRI 295-P.P.</t>
+  </si>
+  <si>
+    <t>NARHARIPURI 296-P.P.</t>
+  </si>
+  <si>
+    <t>NARAHARIPUTI 297-P.P. TOLA</t>
+  </si>
+  <si>
+    <t>SHIVANTOLA 298-P.P. RAI WEST</t>
+  </si>
+  <si>
+    <t>SHIVANRAI 299-P.P. EAST FAKARU</t>
+  </si>
+  <si>
+    <t>RAI KE TOLA 300-P.P. WEST FAKARU</t>
+  </si>
+  <si>
+    <t>RAI KE TOLA EAST 301-P.P.</t>
+  </si>
+  <si>
+    <t>SONBARASA EAST 302-P.P.</t>
+  </si>
+  <si>
+    <t>SONBARASA 303-P.P.</t>
+  </si>
+  <si>
+    <t>SONBARASA WEST 304-P.P.</t>
+  </si>
+  <si>
+    <t>PRITAMCHHAPARA 305-P.P. PRITAM</t>
+  </si>
+  <si>
+    <t>CHHAPARA EAST 306-P.P.</t>
+  </si>
+  <si>
+    <t>RAMNAGAR EAST 307-P.P.</t>
+  </si>
+  <si>
+    <t>RAMNAGAR WEST 308-P.P.</t>
+  </si>
+  <si>
+    <t>MURARPATTI 309-P.P.</t>
+  </si>
+  <si>
+    <t>MURARPATTI 310-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOLCHAUBEY 311-P.P.</t>
+  </si>
+  <si>
+    <t>KI DALAKI 312-P.P.</t>
+  </si>
+  <si>
+    <t>BHAGWANPUR 313-P.P.</t>
+  </si>
+  <si>
+    <t>BHAGWANPUT 314-P.P.</t>
+  </si>
+  <si>
+    <t>IBRAHIMABAD 315-P.P.</t>
+  </si>
+  <si>
+    <t>IBRAHIMABAD 316-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOL 317-JUNIOR HIGH</t>
+  </si>
+  <si>
+    <t>SCHOOLTOLA 318-P.P.</t>
+  </si>
+  <si>
+    <t>FATERAITOLA 319-P.P. NORTH</t>
+  </si>
+  <si>
+    <t>FATERAIBAKULHA 320-P.P. SOUTH</t>
+  </si>
+  <si>
+    <t>P.P. YADAV</t>
+  </si>
+  <si>
+    <t>NAGAR PALTU 322-P.P. CHAND</t>
+  </si>
+  <si>
+    <t>NAGAR THEKAHA 323-P.P. CHAND</t>
+  </si>
+  <si>
+    <t>NORTH THEKAHA 324-P.P.</t>
+  </si>
+  <si>
+    <t>SOUTH LAXMAN 325-P.P.</t>
+  </si>
+  <si>
+    <t>CHHAPARA 326-P.P. NORTH LAXMAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA 327-P.P. SOUTH LAXMAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA 328-P.P. WEST LAXMAN</t>
+  </si>
+  <si>
+    <t>CHHAPARA 329-P.P. EAST PURVI</t>
+  </si>
+  <si>
+    <t>DALJIT TAOLA 330-HIGH SCHOLL</t>
+  </si>
+  <si>
+    <t>JAIPRAKASH 331-P.P.</t>
+  </si>
+  <si>
+    <t>JAIPRAKASH 332-P.P.</t>
+  </si>
+  <si>
+    <t>JAIPRAKASH 333-P.P. DALJIT</t>
+  </si>
+  <si>
+    <t>TOLA WEST 334-P.P. KALI TOLA</t>
+  </si>
+  <si>
+    <t>KASHIRAI 335-P.P. NORTH TOLA</t>
+  </si>
+  <si>
+    <t>KASHIRAI 336-P.P. SOUTH SHANKAR</t>
+  </si>
+  <si>
+    <t>NAGAR KRISHANA 337-P.P.</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM NO. 339</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM NO. 340</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM NO. 341</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM NO. 342</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM NO. 343</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM NO. 344</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 345</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 346</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>NAGAR 338-P.P.BABU KE ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -851,8 +1334,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -868,7 +1359,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -876,12 +1367,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1180,76 +1689,139 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>257</v>
+        <v>418</v>
       </c>
       <c r="D2" t="s">
-        <v>258</v>
+        <v>419</v>
       </c>
       <c r="E2" t="s">
-        <v>259</v>
+        <v>420</v>
       </c>
       <c r="F2" t="s">
-        <v>260</v>
+        <v>421</v>
       </c>
       <c r="G2" t="s">
-        <v>261</v>
+        <v>422</v>
       </c>
       <c r="H2" t="s">
-        <v>262</v>
+        <v>423</v>
       </c>
       <c r="I2" t="s">
-        <v>263</v>
+        <v>424</v>
       </c>
       <c r="J2" t="s">
-        <v>264</v>
+        <v>425</v>
       </c>
       <c r="K2" t="s">
-        <v>265</v>
+        <v>426</v>
       </c>
       <c r="L2" t="s">
-        <v>266</v>
+        <v>427</v>
       </c>
       <c r="M2" t="s">
-        <v>267</v>
+        <v>428</v>
       </c>
       <c r="N2" t="s">
-        <v>268</v>
+        <v>429</v>
       </c>
       <c r="O2" t="s">
-        <v>269</v>
+        <v>430</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>431</v>
       </c>
       <c r="Q2" t="s">
-        <v>271</v>
+        <v>432</v>
       </c>
       <c r="R2" t="s">
-        <v>272</v>
+        <v>433</v>
       </c>
       <c r="S2" t="s">
-        <v>273</v>
+        <v>434</v>
       </c>
       <c r="T2" t="s">
-        <v>274</v>
+        <v>435</v>
       </c>
       <c r="U2" t="s">
-        <v>275</v>
+        <v>436</v>
       </c>
       <c r="V2" t="s">
-        <v>276</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -1257,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>1196</v>
@@ -1325,7 +1897,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>1169</v>
@@ -1393,7 +1965,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>640</v>
@@ -1461,7 +2033,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>647</v>
@@ -1529,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>584</v>
@@ -1597,7 +2169,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>1124</v>
@@ -1665,7 +2237,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>1010</v>
@@ -1733,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>1137</v>
@@ -1801,7 +2373,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>634</v>
@@ -1869,7 +2441,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>512</v>
@@ -1937,7 +2509,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>942</v>
@@ -2005,7 +2577,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>831</v>
@@ -2073,7 +2645,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>928</v>
@@ -2141,7 +2713,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>620</v>
@@ -2209,7 +2781,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <v>622</v>
@@ -2277,7 +2849,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>900</v>
@@ -2345,7 +2917,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>883</v>
@@ -2413,7 +2985,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>929</v>
@@ -2481,7 +3053,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>1028</v>
@@ -2549,7 +3121,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>1086</v>
@@ -2617,7 +3189,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>1019</v>
@@ -2685,7 +3257,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <v>952</v>
@@ -2753,7 +3325,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>1165</v>
@@ -2821,7 +3393,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>1199</v>
@@ -2889,7 +3461,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>1048</v>
@@ -2957,7 +3529,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>734</v>
@@ -3025,7 +3597,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>649</v>
@@ -3093,7 +3665,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>810</v>
@@ -3161,7 +3733,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>505</v>
@@ -3229,7 +3801,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>1007</v>
@@ -3297,7 +3869,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <v>1213</v>
@@ -3365,7 +3937,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C34">
         <v>727</v>
@@ -3433,7 +4005,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>763</v>
@@ -3501,7 +4073,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>842</v>
@@ -3569,7 +4141,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <v>784</v>
@@ -3637,7 +4209,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>551</v>
@@ -3705,7 +4277,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C39">
         <v>570</v>
@@ -3773,7 +4345,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C40">
         <v>1084</v>
@@ -3841,7 +4413,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C41">
         <v>993</v>
@@ -3909,7 +4481,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>970</v>
@@ -3977,7 +4549,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C43">
         <v>1117</v>
@@ -4045,7 +4617,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="C44">
         <v>1068</v>
@@ -4113,7 +4685,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="C45">
         <v>1135</v>
@@ -4181,7 +4753,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C46">
         <v>1166</v>
@@ -4249,7 +4821,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C47">
         <v>804</v>
@@ -4317,7 +4889,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C48">
         <v>664</v>
@@ -4385,7 +4957,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C49">
         <v>615</v>
@@ -4453,7 +5025,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C50">
         <v>611</v>
@@ -4521,7 +5093,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>914</v>
@@ -4589,7 +5161,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="C52">
         <v>1004</v>
@@ -4657,7 +5229,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>984</v>
@@ -4725,7 +5297,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>751</v>
@@ -4793,7 +5365,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>819</v>
@@ -4861,7 +5433,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C56">
         <v>1068</v>
@@ -4929,7 +5501,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>1135</v>
@@ -4997,7 +5569,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C58">
         <v>1178</v>
@@ -5065,7 +5637,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="C59">
         <v>1062</v>
@@ -5133,7 +5705,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C60">
         <v>1156</v>
@@ -5201,7 +5773,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="C61">
         <v>1095</v>
@@ -5269,7 +5841,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="C62">
         <v>799</v>
@@ -5337,7 +5909,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="C63">
         <v>590</v>
@@ -5405,7 +5977,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="C64">
         <v>624</v>
@@ -5473,7 +6045,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="C65">
         <v>1096</v>
@@ -5541,7 +6113,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="C66">
         <v>1094</v>
@@ -5609,7 +6181,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="C67">
         <v>952</v>
@@ -5677,7 +6249,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="C68">
         <v>783</v>
@@ -5745,7 +6317,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>903</v>
@@ -5813,7 +6385,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C70">
         <v>839</v>
@@ -5881,7 +6453,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="C71">
         <v>804</v>
@@ -5949,7 +6521,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="C72">
         <v>843</v>
@@ -6017,7 +6589,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="C73">
         <v>930</v>
@@ -6085,7 +6657,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C74">
         <v>944</v>
@@ -6153,7 +6725,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="C75">
         <v>870</v>
@@ -6221,7 +6793,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="C76">
         <v>851</v>
@@ -6289,7 +6861,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="C77">
         <v>681</v>
@@ -6357,7 +6929,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="C78">
         <v>764</v>
@@ -6425,7 +6997,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="C79">
         <v>821</v>
@@ -6493,7 +7065,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>650</v>
@@ -6561,7 +7133,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="C81">
         <v>972</v>
@@ -6629,7 +7201,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="C82">
         <v>1099</v>
@@ -6697,7 +7269,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="C83">
         <v>1211</v>
@@ -6765,7 +7337,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="C84">
         <v>1146</v>
@@ -6833,7 +7405,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="C85">
         <v>1162</v>
@@ -6901,7 +7473,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="C86">
         <v>837</v>
@@ -6969,7 +7541,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="C87">
         <v>1014</v>
@@ -7037,7 +7609,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="C88">
         <v>766</v>
@@ -7105,7 +7677,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="C89">
         <v>743</v>
@@ -7173,7 +7745,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C90">
         <v>940</v>
@@ -7241,7 +7813,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="C91">
         <v>967</v>
@@ -7309,7 +7881,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="C92">
         <v>666</v>
@@ -7377,7 +7949,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="C93">
         <v>654</v>
@@ -7445,7 +8017,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="C94">
         <v>752</v>
@@ -7513,7 +8085,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="C95">
         <v>907</v>
@@ -7581,7 +8153,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="C96">
         <v>873</v>
@@ -7649,7 +8221,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="C97">
         <v>805</v>
@@ -7717,7 +8289,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C98">
         <v>913</v>
@@ -7785,7 +8357,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="C99">
         <v>925</v>
@@ -7853,7 +8425,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="C100">
         <v>598</v>
@@ -7921,7 +8493,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="C101">
         <v>942</v>
@@ -7989,7 +8561,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="C102">
         <v>865</v>
@@ -8057,7 +8629,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="C103">
         <v>1172</v>
@@ -8125,7 +8697,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="C104">
         <v>1082</v>
@@ -8193,7 +8765,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="C105">
         <v>1159</v>
@@ -8261,7 +8833,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="C106">
         <v>1044</v>
@@ -8329,7 +8901,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>1094</v>
@@ -8397,7 +8969,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="C108">
         <v>1132</v>
@@ -8465,7 +9037,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="C109">
         <v>818</v>
@@ -8533,7 +9105,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="C110">
         <v>616</v>
@@ -8601,7 +9173,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="C111">
         <v>896</v>
@@ -8669,7 +9241,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -8737,7 +9309,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="C113">
         <v>1135</v>
@@ -8805,7 +9377,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="C114">
         <v>660</v>
@@ -8873,7 +9445,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="C115">
         <v>597</v>
@@ -8941,7 +9513,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="C116">
         <v>979</v>
@@ -9009,7 +9581,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="C117">
         <v>995</v>
@@ -9077,7 +9649,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="C118">
         <v>978</v>
@@ -9145,7 +9717,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="C119">
         <v>1055</v>
@@ -9213,7 +9785,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="C120">
         <v>1002</v>
@@ -9281,7 +9853,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C121">
         <v>989</v>
@@ -9349,7 +9921,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="C122">
         <v>680</v>
@@ -9417,7 +9989,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="C123">
         <v>955</v>
@@ -9485,7 +10057,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="C124">
         <v>998</v>
@@ -9553,7 +10125,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="C125">
         <v>710</v>
@@ -9621,7 +10193,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="C126">
         <v>707</v>
@@ -9689,7 +10261,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="C127">
         <v>844</v>
@@ -9757,7 +10329,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="C128">
         <v>797</v>
@@ -9825,7 +10397,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="C129">
         <v>773</v>
@@ -9893,7 +10465,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="C130">
         <v>1002</v>
@@ -9961,7 +10533,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="C131">
         <v>1024</v>
@@ -10029,7 +10601,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="C132">
         <v>950</v>
@@ -10097,7 +10669,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="C133">
         <v>1062</v>
@@ -10165,7 +10737,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="C134">
         <v>1038</v>
@@ -10233,7 +10805,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="C135">
         <v>1005</v>
@@ -10301,7 +10873,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="C136">
         <v>1128</v>
@@ -10369,7 +10941,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="C137">
         <v>560</v>
@@ -10437,7 +11009,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="C138">
         <v>997</v>
@@ -10505,7 +11077,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C139">
         <v>1129</v>
@@ -10573,7 +11145,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="C140">
         <v>991</v>
@@ -10641,7 +11213,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="C141">
         <v>1125</v>
@@ -10709,7 +11281,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="C142">
         <v>732</v>
@@ -10777,7 +11349,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="C143">
         <v>999</v>
@@ -10845,7 +11417,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="C144">
         <v>959</v>
@@ -10913,7 +11485,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="C145">
         <v>1001</v>
@@ -10981,7 +11553,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="C146">
         <v>911</v>
@@ -11049,7 +11621,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="C147">
         <v>1146</v>
@@ -11117,7 +11689,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="C148">
         <v>1106</v>
@@ -11185,7 +11757,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="C149">
         <v>1221</v>
@@ -11253,7 +11825,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="C150">
         <v>970</v>
@@ -11321,7 +11893,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="C151">
         <v>1012</v>
@@ -11389,7 +11961,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="C152">
         <v>949</v>
@@ -11457,7 +12029,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="C153">
         <v>955</v>
@@ -11525,7 +12097,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="C154">
         <v>416</v>
@@ -11593,7 +12165,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="C155">
         <v>694</v>
@@ -11661,7 +12233,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="C156">
         <v>610</v>
@@ -11729,7 +12301,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="C157">
         <v>703</v>
@@ -11797,7 +12369,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="C158">
         <v>932</v>
@@ -11865,7 +12437,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="C159">
         <v>740</v>
@@ -11933,7 +12505,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>86</v>
+        <v>180</v>
       </c>
       <c r="C160">
         <v>920</v>
@@ -12001,7 +12573,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="C161">
         <v>910</v>
@@ -12069,7 +12641,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="C162">
         <v>821</v>
@@ -12137,7 +12709,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="C163">
         <v>880</v>
@@ -12205,7 +12777,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="C164">
         <v>815</v>
@@ -12273,7 +12845,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="C165">
         <v>946</v>
@@ -12341,7 +12913,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>24</v>
+        <v>186</v>
       </c>
       <c r="C166">
         <v>704</v>
@@ -12409,7 +12981,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>25</v>
+        <v>187</v>
       </c>
       <c r="C167">
         <v>641</v>
@@ -12477,7 +13049,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>24</v>
+        <v>188</v>
       </c>
       <c r="C168">
         <v>968</v>
@@ -12545,7 +13117,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="C169">
         <v>937</v>
@@ -12613,7 +13185,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="C170">
         <v>497</v>
@@ -12681,7 +13253,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="C171">
         <v>1200</v>
@@ -12749,7 +13321,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="C172">
         <v>1090</v>
@@ -12817,7 +13389,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="C173">
         <v>1005</v>
@@ -12885,7 +13457,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>112</v>
+        <v>193</v>
       </c>
       <c r="C174">
         <v>794</v>
@@ -12953,7 +13525,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="C175">
         <v>916</v>
@@ -13021,7 +13593,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="C176">
         <v>832</v>
@@ -13089,7 +13661,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>116</v>
+        <v>196</v>
       </c>
       <c r="C177">
         <v>993</v>
@@ -13157,7 +13729,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>117</v>
+        <v>197</v>
       </c>
       <c r="C178">
         <v>1185</v>
@@ -13225,7 +13797,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="C179">
         <v>1235</v>
@@ -13293,7 +13865,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="C180">
         <v>1103</v>
@@ -13361,7 +13933,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="C181">
         <v>928</v>
@@ -13429,7 +14001,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="C182">
         <v>971</v>
@@ -13497,7 +14069,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>121</v>
+        <v>202</v>
       </c>
       <c r="C183">
         <v>1031</v>
@@ -13565,7 +14137,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>122</v>
+        <v>203</v>
       </c>
       <c r="C184">
         <v>738</v>
@@ -13633,7 +14205,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="C185">
         <v>1022</v>
@@ -13701,7 +14273,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>124</v>
+        <v>205</v>
       </c>
       <c r="C186">
         <v>1182</v>
@@ -13769,7 +14341,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>125</v>
+        <v>206</v>
       </c>
       <c r="C187">
         <v>764</v>
@@ -13837,7 +14409,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="C188">
         <v>678</v>
@@ -13905,7 +14477,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>4</v>
+        <v>208</v>
       </c>
       <c r="C189">
         <v>781</v>
@@ -13973,7 +14545,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>86</v>
+        <v>209</v>
       </c>
       <c r="C190">
         <v>674</v>
@@ -14041,7 +14613,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="C191">
         <v>1177</v>
@@ -14109,7 +14681,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>4</v>
+        <v>211</v>
       </c>
       <c r="C192">
         <v>646</v>
@@ -14177,7 +14749,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>86</v>
+        <v>212</v>
       </c>
       <c r="C193">
         <v>610</v>
@@ -14245,7 +14817,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="C194">
         <v>947</v>
@@ -14313,7 +14885,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>127</v>
+        <v>214</v>
       </c>
       <c r="C195">
         <v>588</v>
@@ -14381,7 +14953,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="C196">
         <v>1125</v>
@@ -14449,7 +15021,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>128</v>
+        <v>216</v>
       </c>
       <c r="C197">
         <v>653</v>
@@ -14517,7 +15089,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C198">
         <v>619</v>
@@ -14585,7 +15157,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="C199">
         <v>1031</v>
@@ -14653,7 +15225,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="C200">
         <v>1109</v>
@@ -14721,7 +15293,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -14789,7 +15361,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="C202">
         <v>1057</v>
@@ -14857,7 +15429,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>64</v>
+        <v>221</v>
       </c>
       <c r="C203">
         <v>909</v>
@@ -14925,7 +15497,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>66</v>
+        <v>222</v>
       </c>
       <c r="C204">
         <v>749</v>
@@ -14993,7 +15565,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="C205">
         <v>1141</v>
@@ -15061,7 +15633,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>131</v>
+        <v>224</v>
       </c>
       <c r="C206">
         <v>679</v>
@@ -15129,7 +15701,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="C207">
         <v>1157</v>
@@ -15197,7 +15769,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>133</v>
+        <v>226</v>
       </c>
       <c r="C208">
         <v>927</v>
@@ -15265,7 +15837,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>133</v>
+        <v>227</v>
       </c>
       <c r="C209">
         <v>649</v>
@@ -15333,7 +15905,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="C210">
         <v>907</v>
@@ -15401,7 +15973,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>135</v>
+        <v>229</v>
       </c>
       <c r="C211">
         <v>722</v>
@@ -15469,7 +16041,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>136</v>
+        <v>230</v>
       </c>
       <c r="C212">
         <v>1151</v>
@@ -15537,7 +16109,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>137</v>
+        <v>231</v>
       </c>
       <c r="C213">
         <v>755</v>
@@ -15605,7 +16177,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="C214">
         <v>653</v>
@@ -15673,7 +16245,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>31</v>
+        <v>233</v>
       </c>
       <c r="C215">
         <v>639</v>
@@ -15741,7 +16313,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="C216">
         <v>869</v>
@@ -15809,7 +16381,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>140</v>
+        <v>234</v>
       </c>
       <c r="C217">
         <v>721</v>
@@ -15877,7 +16449,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>32</v>
+        <v>235</v>
       </c>
       <c r="C218">
         <v>888</v>
@@ -15945,7 +16517,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>141</v>
+        <v>236</v>
       </c>
       <c r="C219">
         <v>625</v>
@@ -16013,7 +16585,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>142</v>
+        <v>237</v>
       </c>
       <c r="C220">
         <v>969</v>
@@ -16081,7 +16653,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>143</v>
+        <v>238</v>
       </c>
       <c r="C221">
         <v>813</v>
@@ -16149,7 +16721,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>144</v>
+        <v>239</v>
       </c>
       <c r="C222">
         <v>685</v>
@@ -16217,7 +16789,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="C223">
         <v>1132</v>
@@ -16285,7 +16857,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>146</v>
+        <v>241</v>
       </c>
       <c r="C224">
         <v>785</v>
@@ -16353,7 +16925,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="C225">
         <v>744</v>
@@ -16421,7 +16993,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="C226">
         <v>967</v>
@@ -16489,7 +17061,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="C227">
         <v>1139</v>
@@ -16557,7 +17129,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>109</v>
+        <v>245</v>
       </c>
       <c r="C228">
         <v>978</v>
@@ -16625,7 +17197,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>109</v>
+        <v>246</v>
       </c>
       <c r="C229">
         <v>841</v>
@@ -16693,7 +17265,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>148</v>
+        <v>247</v>
       </c>
       <c r="C230">
         <v>1171</v>
@@ -16761,7 +17333,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>149</v>
+        <v>248</v>
       </c>
       <c r="C231">
         <v>1156</v>
@@ -16829,7 +17401,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="C232">
         <v>1141</v>
@@ -16897,7 +17469,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="C233">
         <v>1044</v>
@@ -16965,7 +17537,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>152</v>
+        <v>251</v>
       </c>
       <c r="C234">
         <v>670</v>
@@ -17033,7 +17605,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>153</v>
+        <v>252</v>
       </c>
       <c r="C235">
         <v>582</v>
@@ -17101,7 +17673,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>154</v>
+        <v>253</v>
       </c>
       <c r="C236">
         <v>957</v>
@@ -17169,7 +17741,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>155</v>
+        <v>254</v>
       </c>
       <c r="C237">
         <v>971</v>
@@ -17237,7 +17809,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="C238">
         <v>855</v>
@@ -17305,7 +17877,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>156</v>
+        <v>256</v>
       </c>
       <c r="C239">
         <v>1012</v>
@@ -17373,7 +17945,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>29</v>
+        <v>257</v>
       </c>
       <c r="C240">
         <v>1080</v>
@@ -17441,7 +18013,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="C241">
         <v>1124</v>
@@ -17509,7 +18081,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>30</v>
+        <v>259</v>
       </c>
       <c r="C242">
         <v>1152</v>
@@ -17577,7 +18149,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>33</v>
+        <v>260</v>
       </c>
       <c r="C243">
         <v>1146</v>
@@ -17645,7 +18217,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>34</v>
+        <v>261</v>
       </c>
       <c r="C244">
         <v>1043</v>
@@ -17713,7 +18285,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>31</v>
+        <v>262</v>
       </c>
       <c r="C245">
         <v>816</v>
@@ -17781,7 +18353,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="C246">
         <v>831</v>
@@ -17849,7 +18421,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>32</v>
+        <v>264</v>
       </c>
       <c r="C247">
         <v>827</v>
@@ -17917,7 +18489,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C248">
         <v>746</v>
@@ -17985,7 +18557,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>31</v>
+        <v>265</v>
       </c>
       <c r="C249">
         <v>889</v>
@@ -18053,7 +18625,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="C250">
         <v>1069</v>
@@ -18121,7 +18693,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>32</v>
+        <v>267</v>
       </c>
       <c r="C251">
         <v>747</v>
@@ -18189,7 +18761,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="C252">
         <v>682</v>
@@ -18257,7 +18829,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>159</v>
+        <v>269</v>
       </c>
       <c r="C253">
         <v>767</v>
@@ -18325,7 +18897,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="C254">
         <v>1098</v>
@@ -18393,7 +18965,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>161</v>
+        <v>271</v>
       </c>
       <c r="C255">
         <v>945</v>
@@ -18461,7 +19033,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>162</v>
+        <v>272</v>
       </c>
       <c r="C256">
         <v>594</v>
@@ -18529,7 +19101,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>89</v>
+        <v>273</v>
       </c>
       <c r="C257">
         <v>1097</v>
@@ -18597,7 +19169,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>163</v>
+        <v>274</v>
       </c>
       <c r="C258">
         <v>1138</v>
@@ -18665,7 +19237,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="C259">
         <v>1115</v>
@@ -18733,7 +19305,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>90</v>
+        <v>276</v>
       </c>
       <c r="C260">
         <v>1093</v>
@@ -18801,7 +19373,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>165</v>
+        <v>277</v>
       </c>
       <c r="C261">
         <v>841</v>
@@ -18869,7 +19441,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>166</v>
+        <v>278</v>
       </c>
       <c r="C262">
         <v>885</v>
@@ -18937,7 +19509,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>167</v>
+        <v>279</v>
       </c>
       <c r="C263">
         <v>808</v>
@@ -19005,7 +19577,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="C264">
         <v>889</v>
@@ -19073,7 +19645,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>26</v>
+        <v>281</v>
       </c>
       <c r="C265">
         <v>970</v>
@@ -19141,7 +19713,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>25</v>
+        <v>282</v>
       </c>
       <c r="C266">
         <v>852</v>
@@ -19209,7 +19781,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>168</v>
+        <v>283</v>
       </c>
       <c r="C267">
         <v>897</v>
@@ -19277,7 +19849,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>169</v>
+        <v>284</v>
       </c>
       <c r="C268">
         <v>913</v>
@@ -19345,7 +19917,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>170</v>
+        <v>285</v>
       </c>
       <c r="C269">
         <v>1105</v>
@@ -19413,7 +19985,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>171</v>
+        <v>286</v>
       </c>
       <c r="C270">
         <v>1210</v>
@@ -19481,7 +20053,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="C271">
         <v>1149</v>
@@ -19549,7 +20121,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>173</v>
+        <v>288</v>
       </c>
       <c r="C272">
         <v>894</v>
@@ -19617,7 +20189,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>174</v>
+        <v>289</v>
       </c>
       <c r="C273">
         <v>875</v>
@@ -19685,7 +20257,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>175</v>
+        <v>290</v>
       </c>
       <c r="C274">
         <v>879</v>
@@ -19753,7 +20325,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>64</v>
+        <v>291</v>
       </c>
       <c r="C275">
         <v>1128</v>
@@ -19821,7 +20393,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>66</v>
+        <v>292</v>
       </c>
       <c r="C276">
         <v>1158</v>
@@ -19889,7 +20461,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>128</v>
+        <v>293</v>
       </c>
       <c r="C277">
         <v>977</v>
@@ -19957,7 +20529,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>129</v>
+        <v>294</v>
       </c>
       <c r="C278">
         <v>693</v>
@@ -20025,7 +20597,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>176</v>
+        <v>295</v>
       </c>
       <c r="C279">
         <v>1022</v>
@@ -20093,7 +20665,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>176</v>
+        <v>296</v>
       </c>
       <c r="C280">
         <v>1110</v>
@@ -20161,7 +20733,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>176</v>
+        <v>297</v>
       </c>
       <c r="C281">
         <v>983</v>
@@ -20229,7 +20801,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>177</v>
+        <v>298</v>
       </c>
       <c r="C282">
         <v>700</v>
@@ -20297,7 +20869,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>178</v>
+        <v>299</v>
       </c>
       <c r="C283">
         <v>670</v>
@@ -20365,7 +20937,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>64</v>
+        <v>300</v>
       </c>
       <c r="C284">
         <v>645</v>
@@ -20433,7 +21005,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>66</v>
+        <v>301</v>
       </c>
       <c r="C285">
         <v>592</v>
@@ -20501,7 +21073,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>29</v>
+        <v>302</v>
       </c>
       <c r="C286">
         <v>716</v>
@@ -20569,7 +21141,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>30</v>
+        <v>303</v>
       </c>
       <c r="C287">
         <v>656</v>
@@ -20637,7 +21209,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>179</v>
+        <v>304</v>
       </c>
       <c r="C288">
         <v>1252</v>
@@ -20705,7 +21277,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>180</v>
+        <v>305</v>
       </c>
       <c r="C289">
         <v>1169</v>
@@ -20773,7 +21345,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>34</v>
+        <v>306</v>
       </c>
       <c r="C290">
         <v>882</v>
@@ -20841,7 +21413,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>37</v>
+        <v>307</v>
       </c>
       <c r="C291">
         <v>836</v>
@@ -20909,7 +21481,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>33</v>
+        <v>308</v>
       </c>
       <c r="C292">
         <v>827</v>
@@ -20977,7 +21549,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>181</v>
+        <v>309</v>
       </c>
       <c r="C293">
         <v>1068</v>
@@ -21045,7 +21617,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>182</v>
+        <v>310</v>
       </c>
       <c r="C294">
         <v>888</v>
@@ -21113,7 +21685,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>183</v>
+        <v>311</v>
       </c>
       <c r="C295">
         <v>942</v>
@@ -21181,7 +21753,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>64</v>
+        <v>312</v>
       </c>
       <c r="C296">
         <v>1136</v>
@@ -21249,7 +21821,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>66</v>
+        <v>313</v>
       </c>
       <c r="C297">
         <v>718</v>
@@ -21317,7 +21889,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>59</v>
+        <v>314</v>
       </c>
       <c r="C298">
         <v>1067</v>
@@ -21385,7 +21957,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>184</v>
+        <v>315</v>
       </c>
       <c r="C299">
         <v>1025</v>
@@ -21453,7 +22025,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>185</v>
+        <v>316</v>
       </c>
       <c r="C300">
         <v>971</v>
@@ -21521,7 +22093,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>186</v>
+        <v>317</v>
       </c>
       <c r="C301">
         <v>1083</v>
@@ -21589,7 +22161,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>187</v>
+        <v>318</v>
       </c>
       <c r="C302">
         <v>978</v>
@@ -21657,7 +22229,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>188</v>
+        <v>319</v>
       </c>
       <c r="C303">
         <v>687</v>
@@ -21725,7 +22297,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>189</v>
+        <v>320</v>
       </c>
       <c r="C304">
         <v>616</v>
@@ -21793,7 +22365,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>190</v>
+        <v>321</v>
       </c>
       <c r="C305">
         <v>897</v>
@@ -21861,7 +22433,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
       <c r="C306">
         <v>917</v>
@@ -21929,7 +22501,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>192</v>
+        <v>323</v>
       </c>
       <c r="C307">
         <v>1063</v>
@@ -21997,7 +22569,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>193</v>
+        <v>324</v>
       </c>
       <c r="C308">
         <v>913</v>
@@ -22065,7 +22637,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>191</v>
+        <v>325</v>
       </c>
       <c r="C309">
         <v>1114</v>
@@ -22133,7 +22705,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>194</v>
+        <v>326</v>
       </c>
       <c r="C310">
         <v>677</v>
@@ -22201,7 +22773,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>195</v>
+        <v>327</v>
       </c>
       <c r="C311">
         <v>579</v>
@@ -22269,7 +22841,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>196</v>
+        <v>328</v>
       </c>
       <c r="C312">
         <v>454</v>
@@ -22337,7 +22909,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>197</v>
+        <v>329</v>
       </c>
       <c r="C313">
         <v>663</v>
@@ -22405,7 +22977,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>198</v>
+        <v>330</v>
       </c>
       <c r="C314">
         <v>636</v>
@@ -22473,7 +23045,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>199</v>
+        <v>331</v>
       </c>
       <c r="C315">
         <v>692</v>
@@ -22541,7 +23113,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>200</v>
+        <v>332</v>
       </c>
       <c r="C316">
         <v>1070</v>
@@ -22609,7 +23181,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>200</v>
+        <v>333</v>
       </c>
       <c r="C317">
         <v>1227</v>
@@ -22677,7 +23249,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>200</v>
+        <v>334</v>
       </c>
       <c r="C318">
         <v>974</v>
@@ -22745,7 +23317,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>201</v>
+        <v>335</v>
       </c>
       <c r="C319">
         <v>989</v>
@@ -22813,7 +23385,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>202</v>
+        <v>336</v>
       </c>
       <c r="C320">
         <v>949</v>
@@ -22881,7 +23453,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>203</v>
+        <v>337</v>
       </c>
       <c r="C321">
         <v>731</v>
@@ -22949,7 +23521,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>204</v>
+        <v>338</v>
       </c>
       <c r="C322">
         <v>1202</v>
@@ -23017,7 +23589,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>205</v>
+        <v>339</v>
       </c>
       <c r="C323">
         <v>1214</v>
@@ -23085,7 +23657,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>206</v>
+        <v>340</v>
       </c>
       <c r="C324">
         <v>1042</v>
@@ -23153,7 +23725,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>207</v>
+        <v>341</v>
       </c>
       <c r="C325">
         <v>1045</v>
@@ -23221,7 +23793,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>207</v>
+        <v>342</v>
       </c>
       <c r="C326">
         <v>1090</v>
@@ -23289,7 +23861,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>208</v>
+        <v>343</v>
       </c>
       <c r="C327">
         <v>1125</v>
@@ -23357,7 +23929,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>208</v>
+        <v>344</v>
       </c>
       <c r="C328">
         <v>1071</v>
@@ -23425,7 +23997,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>206</v>
+        <v>345</v>
       </c>
       <c r="C329">
         <v>894</v>
@@ -23493,7 +24065,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>208</v>
+        <v>346</v>
       </c>
       <c r="C330">
         <v>816</v>
@@ -23561,7 +24133,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>207</v>
+        <v>347</v>
       </c>
       <c r="C331">
         <v>837</v>
@@ -23629,7 +24201,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>209</v>
+        <v>348</v>
       </c>
       <c r="C332">
         <v>1059</v>
@@ -23697,7 +24269,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>210</v>
+        <v>349</v>
       </c>
       <c r="C333">
         <v>738</v>
@@ -23765,7 +24337,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>211</v>
+        <v>350</v>
       </c>
       <c r="C334">
         <v>1215</v>
@@ -23833,7 +24405,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>212</v>
+        <v>351</v>
       </c>
       <c r="C335">
         <v>1044</v>
@@ -23901,7 +24473,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>213</v>
+        <v>352</v>
       </c>
       <c r="C336">
         <v>1097</v>
@@ -23969,7 +24541,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>214</v>
+        <v>353</v>
       </c>
       <c r="C337">
         <v>1143</v>
@@ -24037,7 +24609,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>215</v>
+        <v>354</v>
       </c>
       <c r="C338">
         <v>694</v>
@@ -24105,7 +24677,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>216</v>
+        <v>355</v>
       </c>
       <c r="C339">
         <v>876</v>
@@ -24173,7 +24745,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>217</v>
+        <v>356</v>
       </c>
       <c r="C340">
         <v>816</v>
@@ -24241,7 +24813,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>218</v>
+        <v>357</v>
       </c>
       <c r="C341">
         <v>972</v>
@@ -24309,7 +24881,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>219</v>
+        <v>358</v>
       </c>
       <c r="C342">
         <v>1027</v>
@@ -24377,7 +24949,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>184</v>
+        <v>359</v>
       </c>
       <c r="C343">
         <v>1042</v>
@@ -24445,7 +25017,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>185</v>
+        <v>360</v>
       </c>
       <c r="C344">
         <v>1060</v>
@@ -24513,7 +25085,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>37</v>
+        <v>361</v>
       </c>
       <c r="C345">
         <v>1008</v>
@@ -24581,7 +25153,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>220</v>
+        <v>362</v>
       </c>
       <c r="C346">
         <v>702</v>
@@ -24649,7 +25221,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>221</v>
+        <v>363</v>
       </c>
       <c r="C347">
         <v>1125</v>
@@ -24717,7 +25289,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>222</v>
+        <v>364</v>
       </c>
       <c r="C348">
         <v>870</v>
@@ -24785,7 +25357,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>223</v>
+        <v>365</v>
       </c>
       <c r="C349">
         <v>758</v>
@@ -24853,7 +25425,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>224</v>
+        <v>366</v>
       </c>
       <c r="C350">
         <v>914</v>
@@ -24921,7 +25493,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>225</v>
+        <v>367</v>
       </c>
       <c r="C351">
         <v>718</v>
@@ -24989,7 +25561,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>226</v>
+        <v>368</v>
       </c>
       <c r="C352">
         <v>866</v>
@@ -25057,7 +25629,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="C353">
         <v>877</v>
@@ -25125,7 +25697,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>34</v>
+        <v>370</v>
       </c>
       <c r="C354">
         <v>978</v>
@@ -25193,7 +25765,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>37</v>
+        <v>371</v>
       </c>
       <c r="C355">
         <v>987</v>
@@ -25261,7 +25833,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>37</v>
+        <v>372</v>
       </c>
       <c r="C356">
         <v>979</v>
@@ -25329,7 +25901,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>33</v>
+        <v>373</v>
       </c>
       <c r="C357">
         <v>930</v>
@@ -25397,7 +25969,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>228</v>
+        <v>374</v>
       </c>
       <c r="C358">
         <v>1092</v>
@@ -25465,7 +26037,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>229</v>
+        <v>375</v>
       </c>
       <c r="C359">
         <v>1100</v>
@@ -25533,7 +26105,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>230</v>
+        <v>376</v>
       </c>
       <c r="C360">
         <v>757</v>
@@ -25601,7 +26173,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>231</v>
+        <v>377</v>
       </c>
       <c r="C361">
         <v>830</v>
@@ -25669,7 +26241,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>64</v>
+        <v>378</v>
       </c>
       <c r="C362">
         <v>894</v>
@@ -25737,7 +26309,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>65</v>
+        <v>379</v>
       </c>
       <c r="C363">
         <v>839</v>
@@ -25805,7 +26377,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="C364">
         <v>1014</v>
@@ -25873,7 +26445,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>232</v>
+        <v>381</v>
       </c>
       <c r="C365">
         <v>532</v>
@@ -25941,7 +26513,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>184</v>
+        <v>382</v>
       </c>
       <c r="C366">
         <v>712</v>
@@ -26009,7 +26581,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>185</v>
+        <v>383</v>
       </c>
       <c r="C367">
         <v>650</v>
@@ -26077,7 +26649,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>184</v>
+        <v>384</v>
       </c>
       <c r="C368">
         <v>1087</v>
@@ -26145,7 +26717,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="C369">
         <v>844</v>
@@ -26213,7 +26785,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>219</v>
+        <v>386</v>
       </c>
       <c r="C370">
         <v>1070</v>
@@ -26281,7 +26853,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>233</v>
+        <v>387</v>
       </c>
       <c r="C371">
         <v>1017</v>
@@ -26349,7 +26921,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>234</v>
+        <v>388</v>
       </c>
       <c r="C372">
         <v>1055</v>
@@ -26417,7 +26989,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>235</v>
+        <v>389</v>
       </c>
       <c r="C373">
         <v>1173</v>
@@ -26485,7 +27057,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>236</v>
+        <v>390</v>
       </c>
       <c r="C374">
         <v>1098</v>
@@ -26553,7 +27125,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>236</v>
+        <v>391</v>
       </c>
       <c r="C375">
         <v>1165</v>
@@ -26621,7 +27193,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>237</v>
+        <v>392</v>
       </c>
       <c r="C376">
         <v>860</v>
@@ -26689,7 +27261,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>222</v>
+        <v>393</v>
       </c>
       <c r="C377">
         <v>1146</v>
@@ -26757,7 +27329,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>107</v>
+        <v>394</v>
       </c>
       <c r="C378">
         <v>974</v>
@@ -26825,7 +27397,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>238</v>
+        <v>395</v>
       </c>
       <c r="C379">
         <v>1166</v>
@@ -26893,7 +27465,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>239</v>
+        <v>396</v>
       </c>
       <c r="C380">
         <v>1167</v>
@@ -26961,7 +27533,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>240</v>
+        <v>397</v>
       </c>
       <c r="C381">
         <v>897</v>
@@ -27029,7 +27601,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>241</v>
+        <v>398</v>
       </c>
       <c r="C382">
         <v>963</v>
@@ -27097,7 +27669,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>242</v>
+        <v>399</v>
       </c>
       <c r="C383">
         <v>834</v>
@@ -27165,7 +27737,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>243</v>
+        <v>400</v>
       </c>
       <c r="C384">
         <v>1004</v>
@@ -27233,7 +27805,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>243</v>
+        <v>401</v>
       </c>
       <c r="C385">
         <v>993</v>
@@ -27301,7 +27873,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>243</v>
+        <v>402</v>
       </c>
       <c r="C386">
         <v>934</v>
@@ -27369,7 +27941,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>244</v>
+        <v>403</v>
       </c>
       <c r="C387">
         <v>1022</v>
@@ -27437,7 +28009,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>243</v>
+        <v>404</v>
       </c>
       <c r="C388">
         <v>1099</v>
@@ -27505,7 +28077,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>245</v>
+        <v>405</v>
       </c>
       <c r="C389">
         <v>1160</v>
@@ -27573,7 +28145,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>246</v>
+        <v>406</v>
       </c>
       <c r="C390">
         <v>1151</v>
@@ -27641,7 +28213,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>247</v>
+        <v>407</v>
       </c>
       <c r="C391">
         <v>902</v>
@@ -27709,7 +28281,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>248</v>
+        <v>408</v>
       </c>
       <c r="C392">
         <v>991</v>
@@ -27777,7 +28349,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>249</v>
+        <v>409</v>
       </c>
       <c r="C393">
         <v>1006</v>
@@ -27845,7 +28417,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>250</v>
+        <v>410</v>
       </c>
       <c r="C394">
         <v>900</v>
@@ -27913,7 +28485,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>251</v>
+        <v>411</v>
       </c>
       <c r="C395">
         <v>746</v>
@@ -27981,7 +28553,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>237</v>
+        <v>412</v>
       </c>
       <c r="C396">
         <v>896</v>
@@ -28049,7 +28621,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>252</v>
+        <v>413</v>
       </c>
       <c r="C397">
         <v>964</v>
@@ -28117,7 +28689,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>253</v>
+        <v>414</v>
       </c>
       <c r="C398">
         <v>712</v>
@@ -28185,7 +28757,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>254</v>
+        <v>415</v>
       </c>
       <c r="C399">
         <v>722</v>
@@ -28253,7 +28825,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>255</v>
+        <v>416</v>
       </c>
       <c r="C400">
         <v>668</v>
@@ -28321,7 +28893,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>256</v>
+        <v>417</v>
       </c>
       <c r="C401">
         <v>662</v>
